--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K722"/>
+  <dimension ref="A1:K728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28594,6 +28594,240 @@
         <v>392.76</v>
       </c>
       <c r="K722" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>364.45</v>
+      </c>
+      <c r="C723" t="n">
+        <v>366.6</v>
+      </c>
+      <c r="D723" t="n">
+        <v>368.86</v>
+      </c>
+      <c r="E723" t="n">
+        <v>373.94</v>
+      </c>
+      <c r="F723" t="n">
+        <v>373.35</v>
+      </c>
+      <c r="G723" t="n">
+        <v>365.82</v>
+      </c>
+      <c r="H723" t="n">
+        <v>359.18</v>
+      </c>
+      <c r="I723" t="n">
+        <v>360.17</v>
+      </c>
+      <c r="J723" t="n">
+        <v>392.29</v>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>363.97</v>
+      </c>
+      <c r="C724" t="n">
+        <v>365.67</v>
+      </c>
+      <c r="D724" t="n">
+        <v>367.82</v>
+      </c>
+      <c r="E724" t="n">
+        <v>373.25</v>
+      </c>
+      <c r="F724" t="n">
+        <v>372.65</v>
+      </c>
+      <c r="G724" t="n">
+        <v>365.01</v>
+      </c>
+      <c r="H724" t="n">
+        <v>358.27</v>
+      </c>
+      <c r="I724" t="n">
+        <v>358.66</v>
+      </c>
+      <c r="J724" t="n">
+        <v>392.17</v>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:59:22+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>362.61</v>
+      </c>
+      <c r="C725" t="n">
+        <v>364.57</v>
+      </c>
+      <c r="D725" t="n">
+        <v>366.75</v>
+      </c>
+      <c r="E725" t="n">
+        <v>371.93</v>
+      </c>
+      <c r="F725" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="G725" t="n">
+        <v>363.57</v>
+      </c>
+      <c r="H725" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="I725" t="n">
+        <v>357.21</v>
+      </c>
+      <c r="J725" t="n">
+        <v>392.2</v>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>361.91</v>
+      </c>
+      <c r="C726" t="n">
+        <v>363.52</v>
+      </c>
+      <c r="D726" t="n">
+        <v>366.69</v>
+      </c>
+      <c r="E726" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="F726" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="G726" t="n">
+        <v>362.74</v>
+      </c>
+      <c r="H726" t="n">
+        <v>354.57</v>
+      </c>
+      <c r="I726" t="n">
+        <v>354.87</v>
+      </c>
+      <c r="J726" t="n">
+        <v>394.44</v>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>362.81</v>
+      </c>
+      <c r="C727" t="n">
+        <v>365.21</v>
+      </c>
+      <c r="D727" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="E727" t="n">
+        <v>372.57</v>
+      </c>
+      <c r="F727" t="n">
+        <v>371.56</v>
+      </c>
+      <c r="G727" t="n">
+        <v>363.85</v>
+      </c>
+      <c r="H727" t="n">
+        <v>355.32</v>
+      </c>
+      <c r="I727" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="J727" t="n">
+        <v>395.08</v>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>363.39</v>
+      </c>
+      <c r="C728" t="n">
+        <v>366.02</v>
+      </c>
+      <c r="D728" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="E728" t="n">
+        <v>372.91</v>
+      </c>
+      <c r="F728" t="n">
+        <v>371.69</v>
+      </c>
+      <c r="G728" t="n">
+        <v>364.43</v>
+      </c>
+      <c r="H728" t="n">
+        <v>355.84</v>
+      </c>
+      <c r="I728" t="n">
+        <v>355.48</v>
+      </c>
+      <c r="J728" t="n">
+        <v>395.71</v>
+      </c>
+      <c r="K728" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28610,7 +28844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B734"/>
+  <dimension ref="A1:B740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35953,6 +36187,66 @@
       </c>
       <c r="B734" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-06-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-07-05 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -36121,28 +36415,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2399857272670226</v>
+        <v>0.2260095436121103</v>
       </c>
       <c r="J2" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K2" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07201652890186572</v>
+        <v>0.06469883855147507</v>
       </c>
       <c r="M2" t="n">
-        <v>5.094404021069548</v>
+        <v>5.109567994407421</v>
       </c>
       <c r="N2" t="n">
-        <v>40.18547814245902</v>
+        <v>40.41654986050827</v>
       </c>
       <c r="O2" t="n">
-        <v>6.339201695991304</v>
+        <v>6.357401187632275</v>
       </c>
       <c r="P2" t="n">
-        <v>365.0758924115126</v>
+        <v>365.2265234458981</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36199,28 +36493,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0283453858914978</v>
+        <v>-0.03750357508694703</v>
       </c>
       <c r="J3" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K3" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001143322326788709</v>
+        <v>0.002024811316339914</v>
       </c>
       <c r="M3" t="n">
-        <v>4.940559940504966</v>
+        <v>4.94536772120617</v>
       </c>
       <c r="N3" t="n">
-        <v>38.00926729698872</v>
+        <v>37.9429606472028</v>
       </c>
       <c r="O3" t="n">
-        <v>6.165165634189298</v>
+        <v>6.159785763092966</v>
       </c>
       <c r="P3" t="n">
-        <v>371.4828914844971</v>
+        <v>371.5815932162692</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36277,28 +36571,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03115650556389568</v>
+        <v>0.01902748550108111</v>
       </c>
       <c r="J4" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K4" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001483280060793235</v>
+        <v>0.0005576145269411414</v>
       </c>
       <c r="M4" t="n">
-        <v>4.65048802437509</v>
+        <v>4.665256170170655</v>
       </c>
       <c r="N4" t="n">
-        <v>35.3850590531039</v>
+        <v>35.51707358499294</v>
       </c>
       <c r="O4" t="n">
-        <v>5.948534193656779</v>
+        <v>5.959620255099559</v>
       </c>
       <c r="P4" t="n">
-        <v>373.9995028112948</v>
+        <v>374.130222239027</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36355,28 +36649,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1007106522789665</v>
+        <v>0.09148549544449806</v>
       </c>
       <c r="J5" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K5" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01842682557556952</v>
+        <v>0.01541401641914952</v>
       </c>
       <c r="M5" t="n">
-        <v>4.210571223087895</v>
+        <v>4.224027163280016</v>
       </c>
       <c r="N5" t="n">
-        <v>29.25588437742122</v>
+        <v>29.261259254527</v>
       </c>
       <c r="O5" t="n">
-        <v>5.408870896723384</v>
+        <v>5.409367731493857</v>
       </c>
       <c r="P5" t="n">
-        <v>375.5441402105824</v>
+        <v>375.6435665069867</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36433,28 +36727,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04346596140997416</v>
+        <v>-0.04347374948881225</v>
       </c>
       <c r="J6" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K6" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004013664752835822</v>
+        <v>0.004091080747716358</v>
       </c>
       <c r="M6" t="n">
-        <v>4.03588093558764</v>
+        <v>4.008236942504161</v>
       </c>
       <c r="N6" t="n">
-        <v>25.38640024550433</v>
+        <v>25.18178194703581</v>
       </c>
       <c r="O6" t="n">
-        <v>5.038491862204833</v>
+        <v>5.018145269622613</v>
       </c>
       <c r="P6" t="n">
-        <v>373.1397726112198</v>
+        <v>373.139866628605</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36511,28 +36805,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1252093536045953</v>
+        <v>-0.1259708936390381</v>
       </c>
       <c r="J7" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K7" t="n">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02635445931716052</v>
+        <v>0.02715833378394528</v>
       </c>
       <c r="M7" t="n">
-        <v>4.477513922363657</v>
+        <v>4.448024702164181</v>
       </c>
       <c r="N7" t="n">
-        <v>31.20997236610555</v>
+        <v>30.96189510333593</v>
       </c>
       <c r="O7" t="n">
-        <v>5.586588616150786</v>
+        <v>5.564341389898352</v>
       </c>
       <c r="P7" t="n">
-        <v>368.0445555819656</v>
+        <v>368.0527986722225</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36589,28 +36883,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09515303475201627</v>
+        <v>-0.1009943872552602</v>
       </c>
       <c r="J8" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K8" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01251233684284292</v>
+        <v>0.01429618647870567</v>
       </c>
       <c r="M8" t="n">
-        <v>4.904574367067354</v>
+        <v>4.894382867683201</v>
       </c>
       <c r="N8" t="n">
-        <v>38.69267864316818</v>
+        <v>38.49208189846458</v>
       </c>
       <c r="O8" t="n">
-        <v>6.220343932868036</v>
+        <v>6.204198731380595</v>
       </c>
       <c r="P8" t="n">
-        <v>362.6722434529033</v>
+        <v>362.7352219335688</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36667,28 +36961,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2189708678783089</v>
+        <v>-0.2257280547509666</v>
       </c>
       <c r="J9" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K9" t="n">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05811089118705204</v>
+        <v>0.06241279318692206</v>
       </c>
       <c r="M9" t="n">
-        <v>5.258619972890312</v>
+        <v>5.246147848800243</v>
       </c>
       <c r="N9" t="n">
-        <v>42.08937825206355</v>
+        <v>41.90039659932381</v>
       </c>
       <c r="O9" t="n">
-        <v>6.487632715564557</v>
+        <v>6.473051567794267</v>
       </c>
       <c r="P9" t="n">
-        <v>366.9297337691289</v>
+        <v>367.0026215572287</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36745,28 +37039,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.06139444254662631</v>
+        <v>-0.05191243629597779</v>
       </c>
       <c r="J10" t="n">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="K10" t="n">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003893199343896869</v>
+        <v>0.002825163137163855</v>
       </c>
       <c r="M10" t="n">
-        <v>5.891683455604372</v>
+        <v>5.884198333738921</v>
       </c>
       <c r="N10" t="n">
-        <v>51.97468690832576</v>
+        <v>51.81686010078482</v>
       </c>
       <c r="O10" t="n">
-        <v>7.209347190164014</v>
+        <v>7.198392883191693</v>
       </c>
       <c r="P10" t="n">
-        <v>389.6759974705781</v>
+        <v>389.5733929618322</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36804,7 +37098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K722"/>
+  <dimension ref="A1:K728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77945,6 +78239,348 @@
         </is>
       </c>
     </row>
+    <row r="723">
+      <c r="A723" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>-37.381300931511056,175.93747761444743</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>-37.38199014545291,175.93770041084863</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>-37.3826630044726,175.9379747290247</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>-37.38330837476556,175.93833140286526</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>-37.38394562530244,175.93870794209204</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>-37.38460823811404,175.9390490230541</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>-37.385267078444144,175.93940619425368</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>-37.3859112936796,175.9397772730802</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>-37.38632540639973,175.9405835517657</t>
+        </is>
+      </c>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>-37.381301979006174,175.93747235849804</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>-37.381992419817266,175.9376903089325</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>-37.38266610783442,175.93796365412766</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>-37.38331089958184,175.9383242868904</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>-37.38394856323563,175.9387009517818</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>-37.38461177437824,175.93904102674026</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>-37.38527081446411,175.9393970524782</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>-37.38591821011448,175.93976259860003</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>-37.38632604268481,175.94058245694518</t>
+        </is>
+      </c>
+      <c r="K724" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:59:22+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>-37.38130494690782,175.9374574666405</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>-37.381995109924546,175.93767836042872</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>-37.38266930071525,175.93795225976143</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>-37.38331572966403,175.93831067371977</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>-37.383953809543925,175.9386884690836</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>-37.384618061068856,175.93902681106925</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>-37.385277383288795,175.93938097902452</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>-37.38592485172254,175.93974850720912</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>-37.38632588361354,175.94058273065033</t>
+        </is>
+      </c>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>-37.38130647450354,175.93744980171329</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>-37.38199767775314,175.93766695503788</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>-37.38266947975526,175.93795162082498</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>-37.3833158394386,175.9383103643295</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>-37.38395477486452,175.93868617226693</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>-37.38462168464675,175.93901861731334</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>-37.38528600486804,175.93935988261217</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>-37.38593556990047,175.93972576661426</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>-37.38631400629067,175.94060316729716</t>
+        </is>
+      </c>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>-37.38130451045181,175.9374596566196</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>-37.38199354477137,175.9376853122856</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>-37.38266718207482,175.93795982050923</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>-37.38331338780619,175.93831727404518</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>-37.38395313801654,175.93869006686907</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>-37.38461683865692,175.9390295752277</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>-37.38528292573301,175.93936741704573</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>-37.38593121850394,175.93973499890788</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>-37.38631061276924,175.9406090063379</t>
+        </is>
+      </c>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>-37.38130324472916,175.93746600755892</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>-37.3819915638738,175.93769411072898</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>-37.38266536183407,175.93796631636263</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>-37.38331214369406,175.93832078046785</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>-37.38395259240052,175.93869136506976</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>-37.38461430651771,175.93903530098416</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>-37.385280790865785,175.9393726409193</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>-37.385932775845944,175.93973169471872</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>-37.38630727227132,175.9406147541431</t>
+        </is>
+      </c>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K728"/>
+  <dimension ref="A1:K732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28828,6 +28828,162 @@
         <v>395.71</v>
       </c>
       <c r="K728" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>364.14</v>
+      </c>
+      <c r="C729" t="n">
+        <v>367.13</v>
+      </c>
+      <c r="D729" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="E729" t="n">
+        <v>373.56</v>
+      </c>
+      <c r="F729" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="G729" t="n">
+        <v>364.71</v>
+      </c>
+      <c r="H729" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="I729" t="n">
+        <v>355.25</v>
+      </c>
+      <c r="J729" t="n">
+        <v>396.06</v>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="C730" t="n">
+        <v>369.04</v>
+      </c>
+      <c r="D730" t="n">
+        <v>370.84</v>
+      </c>
+      <c r="E730" t="n">
+        <v>375.7</v>
+      </c>
+      <c r="F730" t="n">
+        <v>372.81</v>
+      </c>
+      <c r="G730" t="n">
+        <v>366.28</v>
+      </c>
+      <c r="H730" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="I730" t="n">
+        <v>356.03</v>
+      </c>
+      <c r="J730" t="n">
+        <v>396.85</v>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="C731" t="n">
+        <v>370.05</v>
+      </c>
+      <c r="D731" t="n">
+        <v>371.99</v>
+      </c>
+      <c r="E731" t="n">
+        <v>376.82</v>
+      </c>
+      <c r="F731" t="n">
+        <v>373.58</v>
+      </c>
+      <c r="G731" t="n">
+        <v>367.2</v>
+      </c>
+      <c r="H731" t="n">
+        <v>357.89</v>
+      </c>
+      <c r="I731" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="J731" t="n">
+        <v>397.41</v>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="C732" t="n">
+        <v>369.78</v>
+      </c>
+      <c r="D732" t="n">
+        <v>371.86</v>
+      </c>
+      <c r="E732" t="n">
+        <v>376.58</v>
+      </c>
+      <c r="F732" t="n">
+        <v>373.1</v>
+      </c>
+      <c r="G732" t="n">
+        <v>366.8</v>
+      </c>
+      <c r="H732" t="n">
+        <v>357.66</v>
+      </c>
+      <c r="I732" t="n">
+        <v>356.71</v>
+      </c>
+      <c r="J732" t="n">
+        <v>396.93</v>
+      </c>
+      <c r="K732" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28844,7 +29000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B740"/>
+  <dimension ref="A1:B744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36247,6 +36403,46 @@
       </c>
       <c r="B740" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B744" t="n">
+        <v>0.26</v>
       </c>
     </row>
   </sheetData>
@@ -36415,28 +36611,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2260095436121103</v>
+        <v>0.2195536196002414</v>
       </c>
       <c r="J2" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K2" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06469883855147507</v>
+        <v>0.06173247874949583</v>
       </c>
       <c r="M2" t="n">
-        <v>5.109567994407421</v>
+        <v>5.108551078876024</v>
       </c>
       <c r="N2" t="n">
-        <v>40.41654986050827</v>
+        <v>40.38182899764549</v>
       </c>
       <c r="O2" t="n">
-        <v>6.357401187632275</v>
+        <v>6.354669857486343</v>
       </c>
       <c r="P2" t="n">
-        <v>365.2265234458981</v>
+        <v>365.2963203109163</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36493,28 +36689,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03750357508694703</v>
+        <v>-0.03924405850606986</v>
       </c>
       <c r="J3" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K3" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002024811316339914</v>
+        <v>0.002243264912969445</v>
       </c>
       <c r="M3" t="n">
-        <v>4.94536772120617</v>
+        <v>4.926910157482896</v>
       </c>
       <c r="N3" t="n">
-        <v>37.9429606472028</v>
+        <v>37.75580622876456</v>
       </c>
       <c r="O3" t="n">
-        <v>6.159785763092966</v>
+        <v>6.144575349750751</v>
       </c>
       <c r="P3" t="n">
-        <v>371.5815932162692</v>
+        <v>371.6004012959651</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36571,28 +36767,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01902748550108111</v>
+        <v>0.01490222972064404</v>
       </c>
       <c r="J4" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K4" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005576145269411414</v>
+        <v>0.0003456000200621201</v>
       </c>
       <c r="M4" t="n">
-        <v>4.665256170170655</v>
+        <v>4.657968476336541</v>
       </c>
       <c r="N4" t="n">
-        <v>35.51707358499294</v>
+        <v>35.40547665789025</v>
       </c>
       <c r="O4" t="n">
-        <v>5.959620255099559</v>
+        <v>5.950250134060774</v>
       </c>
       <c r="P4" t="n">
-        <v>374.130222239027</v>
+        <v>374.1748143779213</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36649,28 +36845,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09148549544449806</v>
+        <v>0.0887879185044162</v>
       </c>
       <c r="J5" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K5" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01541401641914952</v>
+        <v>0.0146909830862163</v>
       </c>
       <c r="M5" t="n">
-        <v>4.224027163280016</v>
+        <v>4.214968426164595</v>
       </c>
       <c r="N5" t="n">
-        <v>29.261259254527</v>
+        <v>29.14212139695809</v>
       </c>
       <c r="O5" t="n">
-        <v>5.409367731493857</v>
+        <v>5.39834431997053</v>
       </c>
       <c r="P5" t="n">
-        <v>375.6435665069867</v>
+        <v>375.6727216489638</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36727,28 +36923,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04347374948881225</v>
+        <v>-0.04246153813866636</v>
       </c>
       <c r="J6" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K6" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004091080747716358</v>
+        <v>0.003951421327461957</v>
       </c>
       <c r="M6" t="n">
-        <v>4.008236942504161</v>
+        <v>3.990801142988927</v>
       </c>
       <c r="N6" t="n">
-        <v>25.18178194703581</v>
+        <v>25.0501562886064</v>
       </c>
       <c r="O6" t="n">
-        <v>5.018145269622613</v>
+        <v>5.005013115727709</v>
       </c>
       <c r="P6" t="n">
-        <v>373.139866628605</v>
+        <v>373.128918080018</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36805,28 +37001,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1259708936390381</v>
+        <v>-0.1242085676577828</v>
       </c>
       <c r="J7" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K7" t="n">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02715833378394528</v>
+        <v>0.02673208501041313</v>
       </c>
       <c r="M7" t="n">
-        <v>4.448024702164181</v>
+        <v>4.432712909887455</v>
       </c>
       <c r="N7" t="n">
-        <v>30.96189510333593</v>
+        <v>30.81068036277943</v>
       </c>
       <c r="O7" t="n">
-        <v>5.564341389898352</v>
+        <v>5.550736920696155</v>
       </c>
       <c r="P7" t="n">
-        <v>368.0527986722225</v>
+        <v>368.0336717765538</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36883,28 +37079,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1009943872552602</v>
+        <v>-0.1041747556089278</v>
       </c>
       <c r="J8" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K8" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01429618647870567</v>
+        <v>0.01536636264816116</v>
       </c>
       <c r="M8" t="n">
-        <v>4.894382867683201</v>
+        <v>4.884142199142114</v>
       </c>
       <c r="N8" t="n">
-        <v>38.49208189846458</v>
+        <v>38.32837310080033</v>
       </c>
       <c r="O8" t="n">
-        <v>6.204198731380595</v>
+        <v>6.190991285795864</v>
       </c>
       <c r="P8" t="n">
-        <v>362.7352219335688</v>
+        <v>362.7696032690049</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36961,28 +37157,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2257280547509666</v>
+        <v>-0.2309217728296013</v>
       </c>
       <c r="J9" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K9" t="n">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06241279318692206</v>
+        <v>0.06571485337297267</v>
       </c>
       <c r="M9" t="n">
-        <v>5.246147848800243</v>
+        <v>5.240942813508855</v>
       </c>
       <c r="N9" t="n">
-        <v>41.90039659932381</v>
+        <v>41.79168378550905</v>
       </c>
       <c r="O9" t="n">
-        <v>6.473051567794267</v>
+        <v>6.464648775108286</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0026215572287</v>
+        <v>367.0587975701981</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37039,28 +37235,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05191243629597779</v>
+        <v>-0.04230895963577221</v>
       </c>
       <c r="J10" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="K10" t="n">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002825163137163855</v>
+        <v>0.001887227231577415</v>
       </c>
       <c r="M10" t="n">
-        <v>5.884198333738921</v>
+        <v>5.894431231183535</v>
       </c>
       <c r="N10" t="n">
-        <v>51.81686010078482</v>
+        <v>51.93560822930444</v>
       </c>
       <c r="O10" t="n">
-        <v>7.198392883191693</v>
+        <v>7.206636401907928</v>
       </c>
       <c r="P10" t="n">
-        <v>389.5733929618322</v>
+        <v>389.4691605207065</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37098,7 +37294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K728"/>
+  <dimension ref="A1:K732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78581,6 +78777,234 @@
         </is>
       </c>
     </row>
+    <row r="729">
+      <c r="A729" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>-37.38130160801835,175.93747421998012</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>-37.381988849309415,175.93770616785432</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>-37.38266270607237,175.93797579391855</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>-37.38330976524415,175.93832748392268</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>-37.38395108146376,175.93869496008688</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>-37.384613084105574,175.9390380651423</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>-37.38527939499093,175.93937605652877</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>-37.38593382934194,175.93972945953186</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>-37.386305416439036,175.940617947368</t>
+        </is>
+      </c>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>-37.38129859646901,175.9374893308341</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>-37.381984178299454,175.93772691479745</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>-37.38265709614635,175.93799581392207</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>-37.38330193465261,175.93834955375533</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>-37.38394789170807,175.93870254956707</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>-37.38460622986501,175.93905356417028</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>-37.38527664429612,175.93938278728822</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>-37.3859302566162,175.9397370397305</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>-37.38630122756016,175.94062515493218</t>
+        </is>
+      </c>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>-37.38129728709913,175.9374959007702</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>-37.38198170828751,175.93773788569297</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>-37.38265366454107,175.93800806019925</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>-37.38329783639753,175.93836110432002</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>-37.38394465998145,175.93871023890813</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>-37.38460221336647,175.93906264640185</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>-37.385272374560145,175.9393932350332</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>-37.385925996827226,175.93974607765873</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>-37.38629825822803,175.94063026409106</t>
+        </is>
+      </c>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:05:56+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>-37.38129728709913,175.9374959007702</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>-37.381982368587835,175.9377349528794</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>-37.382654052461724,175.93800667583753</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>-37.383298714595135,175.93835862919914</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>-37.38394667456433,175.93870544555276</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>-37.38460395967026,175.93905869760562</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>-37.385273318828766,175.93939092447434</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>-37.38592714193185,175.93974364810822</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>-37.38630080336987,175.94062588481205</t>
+        </is>
+      </c>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0203/nzd0203.xlsx
+++ b/data/nzd0203/nzd0203.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K732"/>
+  <dimension ref="A1:K734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28984,6 +28984,84 @@
         <v>396.93</v>
       </c>
       <c r="K732" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>366.12</v>
+      </c>
+      <c r="C733" t="n">
+        <v>369.83</v>
+      </c>
+      <c r="D733" t="n">
+        <v>371.9</v>
+      </c>
+      <c r="E733" t="n">
+        <v>376.89</v>
+      </c>
+      <c r="F733" t="n">
+        <v>373.08</v>
+      </c>
+      <c r="G733" t="n">
+        <v>366.88</v>
+      </c>
+      <c r="H733" t="n">
+        <v>357.9</v>
+      </c>
+      <c r="I733" t="n">
+        <v>357.06</v>
+      </c>
+      <c r="J733" t="n">
+        <v>396.05</v>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>366.22</v>
+      </c>
+      <c r="C734" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="D734" t="n">
+        <v>371.88</v>
+      </c>
+      <c r="E734" t="n">
+        <v>377.48</v>
+      </c>
+      <c r="F734" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="G734" t="n">
+        <v>367.31</v>
+      </c>
+      <c r="H734" t="n">
+        <v>358.46</v>
+      </c>
+      <c r="I734" t="n">
+        <v>357.32</v>
+      </c>
+      <c r="J734" t="n">
+        <v>397.68</v>
+      </c>
+      <c r="K734" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29000,7 +29078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B744"/>
+  <dimension ref="A1:B746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36443,6 +36521,26 @@
       </c>
       <c r="B744" t="n">
         <v>0.26</v>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B745" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B746" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -36611,28 +36709,28 @@
         <v>0.0888</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2195536196002414</v>
+        <v>0.2167540747286902</v>
       </c>
       <c r="J2" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K2" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06173247874949583</v>
+        <v>0.06051950136238349</v>
       </c>
       <c r="M2" t="n">
-        <v>5.108551078876024</v>
+        <v>5.106255850368697</v>
       </c>
       <c r="N2" t="n">
-        <v>40.38182899764549</v>
+        <v>40.34083935720355</v>
       </c>
       <c r="O2" t="n">
-        <v>6.354669857486343</v>
+        <v>6.351443879717709</v>
       </c>
       <c r="P2" t="n">
-        <v>365.2963203109163</v>
+        <v>365.3267133488594</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36689,28 +36787,28 @@
         <v>0.0893</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03924405850606986</v>
+        <v>-0.0394521180535611</v>
       </c>
       <c r="J3" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K3" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002243264912969445</v>
+        <v>0.002281191195252497</v>
       </c>
       <c r="M3" t="n">
-        <v>4.926910157482896</v>
+        <v>4.914484038304729</v>
       </c>
       <c r="N3" t="n">
-        <v>37.75580622876456</v>
+        <v>37.65347661472934</v>
       </c>
       <c r="O3" t="n">
-        <v>6.144575349750751</v>
+        <v>6.136242874490003</v>
       </c>
       <c r="P3" t="n">
-        <v>371.6004012959651</v>
+        <v>371.6026583169922</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36767,28 +36865,28 @@
         <v>0.1088</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01490222972064404</v>
+        <v>0.01341378804112223</v>
       </c>
       <c r="J4" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K4" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003456000200621201</v>
+        <v>0.0002816269315611963</v>
       </c>
       <c r="M4" t="n">
-        <v>4.657968476336541</v>
+        <v>4.651844247065962</v>
       </c>
       <c r="N4" t="n">
-        <v>35.40547665789025</v>
+        <v>35.3284293797204</v>
       </c>
       <c r="O4" t="n">
-        <v>5.950250134060774</v>
+        <v>5.943772318967173</v>
       </c>
       <c r="P4" t="n">
-        <v>374.1748143779213</v>
+        <v>374.1909737140396</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36845,28 +36943,28 @@
         <v>0.1105</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0887879185044162</v>
+        <v>0.08829686873999192</v>
       </c>
       <c r="J5" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K5" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0146909830862163</v>
+        <v>0.01461983465303529</v>
       </c>
       <c r="M5" t="n">
-        <v>4.214968426164595</v>
+        <v>4.205996745420405</v>
       </c>
       <c r="N5" t="n">
-        <v>29.14212139695809</v>
+        <v>29.06497281103757</v>
       </c>
       <c r="O5" t="n">
-        <v>5.39834431997053</v>
+        <v>5.391194006065592</v>
       </c>
       <c r="P5" t="n">
-        <v>375.6727216489638</v>
+        <v>375.6780511704389</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36923,28 +37021,28 @@
         <v>0.108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04246153813866636</v>
+        <v>-0.0417114114188649</v>
       </c>
       <c r="J6" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K6" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003951421327461957</v>
+        <v>0.003836586186983015</v>
       </c>
       <c r="M6" t="n">
-        <v>3.990801142988927</v>
+        <v>3.983222969600508</v>
       </c>
       <c r="N6" t="n">
-        <v>25.0501562886064</v>
+        <v>24.98695648261536</v>
       </c>
       <c r="O6" t="n">
-        <v>5.005013115727709</v>
+        <v>4.998695478083794</v>
       </c>
       <c r="P6" t="n">
-        <v>373.128918080018</v>
+        <v>373.1207729337453</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37001,28 +37099,28 @@
         <v>0.1305</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1242085676577828</v>
+        <v>-0.1228664416187834</v>
       </c>
       <c r="J7" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K7" t="n">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02673208501041313</v>
+        <v>0.02631932413334226</v>
       </c>
       <c r="M7" t="n">
-        <v>4.432712909887455</v>
+        <v>4.42752287664182</v>
       </c>
       <c r="N7" t="n">
-        <v>30.81068036277943</v>
+        <v>30.74240629106801</v>
       </c>
       <c r="O7" t="n">
-        <v>5.550736920696155</v>
+        <v>5.544583509251891</v>
       </c>
       <c r="P7" t="n">
-        <v>368.0336717765538</v>
+        <v>368.0190518275288</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37079,28 +37177,28 @@
         <v>0.1514</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1041747556089278</v>
+        <v>-0.1051581034150661</v>
       </c>
       <c r="J8" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K8" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01536636264816116</v>
+        <v>0.0157462543074316</v>
       </c>
       <c r="M8" t="n">
-        <v>4.884142199142114</v>
+        <v>4.875875691816903</v>
       </c>
       <c r="N8" t="n">
-        <v>38.32837310080033</v>
+        <v>38.2325500118603</v>
       </c>
       <c r="O8" t="n">
-        <v>6.190991285795864</v>
+        <v>6.18324752956408</v>
       </c>
       <c r="P8" t="n">
-        <v>362.7696032690049</v>
+        <v>362.7802774928713</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37157,28 +37255,28 @@
         <v>0.1384</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2309217728296013</v>
+        <v>-0.2329338421903106</v>
       </c>
       <c r="J9" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="K9" t="n">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06571485337297267</v>
+        <v>0.06712457842582031</v>
       </c>
       <c r="M9" t="n">
-        <v>5.240942813508855</v>
+        <v>5.235632146835735</v>
       </c>
       <c r="N9" t="n">
-        <v>41.79168378550905</v>
+        <v>41.71331288845803</v>
       </c>
       <c r="O9" t="n">
-        <v>6.464648775108286</v>
+        <v>6.458584433794918</v>
       </c>
       <c r="P9" t="n">
-        <v>367.0587975701981</v>
+        <v>367.0806507137671</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37235,28 +37333,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04230895963577221</v>
+        <v>-0.03756144706341891</v>
       </c>
       <c r="J10" t="n">
+        <v>733</v>
+      </c>
+      <c r="K10" t="n">
         <v>731</v>
       </c>
-      <c r="K10" t="n">
-        <v>729</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.001887227231577415</v>
+        <v>0.001491644111127566</v>
       </c>
       <c r="M10" t="n">
-        <v>5.894431231183535</v>
+        <v>5.899379850966222</v>
       </c>
       <c r="N10" t="n">
-        <v>51.93560822930444</v>
+        <v>51.99291613154186</v>
       </c>
       <c r="O10" t="n">
-        <v>7.206636401907928</v>
+        <v>7.210611356295793</v>
       </c>
       <c r="P10" t="n">
-        <v>389.4691605207065</v>
+        <v>389.41742131294</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37294,7 +37392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K732"/>
+  <dimension ref="A1:K734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79005,6 +79103,120 @@
         </is>
       </c>
     </row>
+    <row r="733">
+      <c r="A733" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>-37.38129728709913,175.9374959007702</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>-37.38198224631002,175.93773549599302</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>-37.382653933101516,175.938007101795</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>-37.38329758025655,175.9383618262303</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>-37.38394675850528,175.93870524582962</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>-37.38460361040951,175.9390594873649</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>-37.385272333505,175.93939333549227</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>-37.38592553878535,175.93974704947888</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>-37.38630546946282,175.940617856133</t>
+        </is>
+      </c>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>-37.38129706887077,175.93749699575952</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>-37.38198060778683,175.93774277371548</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>-37.38265399278162,175.93800688881626</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>-37.38329542135384,175.9383679109022</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>-37.383944576040484,175.93871043863126</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>-37.3846017331329,175.9390637323208</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>-37.385270034416045,175.9393989612006</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>-37.385924347876475,175.93974957621128</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>-37.3862968265857,175.9406327274354</t>
+        </is>
+      </c>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
